--- a/product_order_forms/013_smart_robot_maintenance_kit_order_form--product_order_forms.xlsx
+++ b/product_order_forms/013_smart_robot_maintenance_kit_order_form--product_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'general_inspection'}</t>
+          <t>general_inspection</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'General Inspection'}</t>
+          <t>General Inspection</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'diagnostic_test'}</t>
+          <t>diagnostic_test</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Diagnostic Test'}</t>
+          <t>Diagnostic Test</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'complete_repair'}</t>
+          <t>complete_repair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Complete Repair'}</t>
+          <t>Complete Repair</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'parts_replacement'}</t>
+          <t>parts_replacement</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Parts Replacement'}</t>
+          <t>Parts Replacement</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'preventative_maintenance'}</t>
+          <t>preventative_maintenance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Preventative Maintenance'}</t>
+          <t>Preventative Maintenance</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
